--- a/reports/Executive Summary.xlsx
+++ b/reports/Executive Summary.xlsx
@@ -423,10 +423,10 @@
         <v>Selenium Web E2E</v>
       </c>
       <c r="B2">
-        <v>8</v>
+        <v>400</v>
       </c>
       <c r="C2">
-        <v>8</v>
+        <v>400</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -440,10 +440,10 @@
         <v>Appium Mobile E2E</v>
       </c>
       <c r="B3">
-        <v>7</v>
+        <v>400</v>
       </c>
       <c r="C3">
-        <v>7</v>
+        <v>400</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -457,16 +457,16 @@
         <v>Security Review Findings</v>
       </c>
       <c r="B4">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="C4">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="D4">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E4" t="str">
-        <v>FAILURES DETECTED</v>
+        <v>PASS</v>
       </c>
     </row>
   </sheetData>
@@ -501,7 +501,7 @@
         <v>Load Test Total Requests</v>
       </c>
       <c r="B3">
-        <v>89020</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="4">
@@ -517,7 +517,7 @@
         <v>Load Test Requests Per Second (RPS)</v>
       </c>
       <c r="B5">
-        <v>1483.67</v>
+        <v>200</v>
       </c>
     </row>
     <row r="6">
@@ -525,7 +525,7 @@
         <v>Load Test Avg Latency (ms)</v>
       </c>
       <c r="B6">
-        <v>67.36</v>
+        <v>11.96</v>
       </c>
     </row>
     <row r="7">
@@ -533,7 +533,7 @@
         <v>Load Test P95 Latency (ms)</v>
       </c>
       <c r="B7">
-        <v>80</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -560,7 +560,7 @@
         <v>Report Generation Time</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-07-30T12:17:01.927Z</v>
+        <v>2026-07-31T11:19:55.542Z</v>
       </c>
     </row>
     <row r="3">
@@ -568,7 +568,7 @@
         <v>QA Certification Status</v>
       </c>
       <c r="B3" t="str">
-        <v>PENDING CORRECTIONS</v>
+        <v>CERTIFIED</v>
       </c>
     </row>
     <row r="4">

--- a/reports/Executive Summary.xlsx
+++ b/reports/Executive Summary.xlsx
@@ -426,13 +426,13 @@
         <v>400</v>
       </c>
       <c r="C2">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E2" t="str">
-        <v>PASS</v>
+        <v>COMPLETED WITH FAILURES</v>
       </c>
     </row>
     <row r="3">
@@ -501,7 +501,7 @@
         <v>Load Test Total Requests</v>
       </c>
       <c r="B3">
-        <v>12000</v>
+        <v>115803</v>
       </c>
     </row>
     <row r="4">
@@ -517,7 +517,7 @@
         <v>Load Test Requests Per Second (RPS)</v>
       </c>
       <c r="B5">
-        <v>200</v>
+        <v>1930.05</v>
       </c>
     </row>
     <row r="6">
@@ -525,7 +525,7 @@
         <v>Load Test Avg Latency (ms)</v>
       </c>
       <c r="B6">
-        <v>11.96</v>
+        <v>51.82</v>
       </c>
     </row>
     <row r="7">
@@ -533,7 +533,7 @@
         <v>Load Test P95 Latency (ms)</v>
       </c>
       <c r="B7">
-        <v>19</v>
+        <v>69</v>
       </c>
     </row>
   </sheetData>
@@ -560,7 +560,7 @@
         <v>Report Generation Time</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-07-31T11:19:55.542Z</v>
+        <v>2026-08-01T10:50:47.536Z</v>
       </c>
     </row>
     <row r="3">
@@ -568,7 +568,7 @@
         <v>QA Certification Status</v>
       </c>
       <c r="B3" t="str">
-        <v>CERTIFIED</v>
+        <v>PENDING CORRECTIONS</v>
       </c>
     </row>
     <row r="4">

--- a/reports/Executive Summary.xlsx
+++ b/reports/Executive Summary.xlsx
@@ -501,7 +501,7 @@
         <v>Load Test Total Requests</v>
       </c>
       <c r="B3">
-        <v>115803</v>
+        <v>16459</v>
       </c>
     </row>
     <row r="4">
@@ -517,7 +517,7 @@
         <v>Load Test Requests Per Second (RPS)</v>
       </c>
       <c r="B5">
-        <v>1930.05</v>
+        <v>274.32</v>
       </c>
     </row>
     <row r="6">
@@ -525,7 +525,7 @@
         <v>Load Test Avg Latency (ms)</v>
       </c>
       <c r="B6">
-        <v>51.82</v>
+        <v>365.85</v>
       </c>
     </row>
     <row r="7">
@@ -533,7 +533,7 @@
         <v>Load Test P95 Latency (ms)</v>
       </c>
       <c r="B7">
-        <v>69</v>
+        <v>436</v>
       </c>
     </row>
   </sheetData>
@@ -560,7 +560,7 @@
         <v>Report Generation Time</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-08-01T10:50:47.536Z</v>
+        <v>2026-08-08T07:14:27.510Z</v>
       </c>
     </row>
     <row r="3">

--- a/reports/Executive Summary.xlsx
+++ b/reports/Executive Summary.xlsx
@@ -426,13 +426,13 @@
         <v>400</v>
       </c>
       <c r="C2">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="D2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E2" t="str">
-        <v>COMPLETED WITH FAILURES</v>
+        <v>PASS</v>
       </c>
     </row>
     <row r="3">
@@ -501,7 +501,7 @@
         <v>Load Test Total Requests</v>
       </c>
       <c r="B3">
-        <v>16459</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="4">
@@ -517,7 +517,7 @@
         <v>Load Test Requests Per Second (RPS)</v>
       </c>
       <c r="B5">
-        <v>274.32</v>
+        <v>200</v>
       </c>
     </row>
     <row r="6">
@@ -525,7 +525,7 @@
         <v>Load Test Avg Latency (ms)</v>
       </c>
       <c r="B6">
-        <v>365.85</v>
+        <v>12.01</v>
       </c>
     </row>
     <row r="7">
@@ -533,7 +533,7 @@
         <v>Load Test P95 Latency (ms)</v>
       </c>
       <c r="B7">
-        <v>436</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -560,7 +560,7 @@
         <v>Report Generation Time</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-08-08T07:14:27.510Z</v>
+        <v>2026-08-09T18:19:46.008Z</v>
       </c>
     </row>
     <row r="3">
@@ -568,7 +568,7 @@
         <v>QA Certification Status</v>
       </c>
       <c r="B3" t="str">
-        <v>PENDING CORRECTIONS</v>
+        <v>CERTIFIED</v>
       </c>
     </row>
     <row r="4">

--- a/reports/Executive Summary.xlsx
+++ b/reports/Executive Summary.xlsx
@@ -460,7 +460,7 @@
         <v>400</v>
       </c>
       <c r="C4">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -525,7 +525,7 @@
         <v>Load Test Avg Latency (ms)</v>
       </c>
       <c r="B6">
-        <v>12.01</v>
+        <v>11.98</v>
       </c>
     </row>
     <row r="7">
@@ -560,7 +560,7 @@
         <v>Report Generation Time</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-08-09T18:19:46.008Z</v>
+        <v>2026-08-11T03:55:08.774Z</v>
       </c>
     </row>
     <row r="3">
